--- a/docs/station4/バリデーション設計書.xlsx
+++ b/docs/station4/バリデーション設計書.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11040" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="11540" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ユーザー登録画面" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
   <si>
     <t>項目</t>
   </si>
@@ -47,11 +47,14 @@
   </si>
   <si>
     <t>・必須
-・8文字以上50文字以下
-・英数字のみ</t>
-  </si>
-  <si>
-    <t>「ユーザーIDを8文字以上50文字以下で英数字のみで入力してください」</t>
+・5文字以上
+・半角英数字とアンダースコア（_）のみ
+・unique</t>
+  </si>
+  <si>
+    <t>「ユーザーIDは5文字以上で指定してください」
+「ユーザーIDは既に他のユーザーに使用されています」
+「ユーザーIDは半角英数字とアンダースコア（_）のみ使用できます」</t>
   </si>
   <si>
     <t>メールアドレス</t>
@@ -59,10 +62,11 @@
   <si>
     <t>・必須
 ・「@」の前後に文字がある
-・ドメインに「.」が含まれる</t>
-  </si>
-  <si>
-    <t>「有効なメールアドレスを入力してください」</t>
+・ドメインに「.」が含まれる
+・unique</t>
+  </si>
+  <si>
+    <t>「メールアドレスに正しい形式を指定してください」</t>
   </si>
   <si>
     <t>パスワード</t>
@@ -73,10 +77,9 @@
 ・英大文字 / 英小文字 / 数字 / 記号 のうち3種類以上</t>
   </si>
   <si>
-    <t>「パスワードは8文字以上で入力してください」
-「英大文字・英小文字・数字・記号のうち3種類以上を含めてください」
-「パスワードに空白は使用できません」
-「パスワードに全角文字は使用できません」</t>
+    <t xml:space="preserve">「パスワードは8文字以上で指定してください」
+「パスワードは英大文字・英小文字・数字・記号のうち3種類以上を含む必要があります。」
+</t>
   </si>
   <si>
     <t>ユーザー名</t>
@@ -86,67 +89,115 @@
 ・50文字以下</t>
   </si>
   <si>
-    <t>「ユーザー名は50文字以下で英数字のみで入力してください」</t>
+    <t>「ユーザー名は50文字以下で入力してください」</t>
   </si>
   <si>
     <t>プロフィール写真</t>
-  </si>
-  <si>
-    <t>・任意
-・2MB以内
-・ファイル形式
-(jpg, jpeg, png, webp)</t>
-  </si>
-  <si>
-    <t>「jpg, jpeg, png, webp 形式の画像のみ使用できます」</t>
-  </si>
-  <si>
-    <t>自己紹介</t>
-  </si>
-  <si>
-    <t>・任意
-・最大1000文字</t>
-  </si>
-  <si>
-    <t>「自己紹介は1000文字以内で入力してください」</t>
-  </si>
-  <si>
-    <t>タイトル</t>
-  </si>
-  <si>
-    <t>・必須
-・50文字以内</t>
-  </si>
-  <si>
-    <t>「タイトルを50文字以内で入力してください」</t>
-  </si>
-  <si>
-    <t>サブタイトル</t>
-  </si>
-  <si>
-    <t>・任意
-・50文字以内</t>
-  </si>
-  <si>
-    <t>「サブタイトルは50文字以内で入力してください」</t>
-  </si>
-  <si>
-    <t>本文</t>
-  </si>
-  <si>
-    <t>・任意
-・1000文字以内</t>
-  </si>
-  <si>
-    <t>「本文は1000文字以内で入力してください」</t>
-  </si>
-  <si>
-    <t>写真</t>
   </si>
   <si>
     <t>・任意
 ・ファイル形式
 (jpg, jpeg, png, webp)</t>
+  </si>
+  <si>
+    <t>自己紹介</t>
+  </si>
+  <si>
+    <t>・任意
+・最大1000文字</t>
+  </si>
+  <si>
+    <t>「自己紹介は1000文字以内で入力してください」</t>
+  </si>
+  <si>
+    <t>訪れた国</t>
+  </si>
+  <si>
+    <t>・任意</t>
+  </si>
+  <si>
+    <t>タイトル</t>
+  </si>
+  <si>
+    <t>・必須
+・50文字以内</t>
+  </si>
+  <si>
+    <t>「タイトルは50文字以内で指定してください」</t>
+  </si>
+  <si>
+    <t>サブタイトル</t>
+  </si>
+  <si>
+    <t>・任意
+・50文字以内</t>
+  </si>
+  <si>
+    <t>「サブタイトルは50文字以内で指定してください」</t>
+  </si>
+  <si>
+    <t>タビ概要</t>
+  </si>
+  <si>
+    <t>・任意
+・1000文字以内</t>
+  </si>
+  <si>
+    <t>「タビ概要は1000文字以内で指定してください」</t>
+  </si>
+  <si>
+    <t>写真</t>
+  </si>
+  <si>
+    <t>・任意
+・ファイル形式
+(jpg, jpeg, png, webp)
+・上限８枚</t>
+  </si>
+  <si>
+    <t>「写真は最大８枚までです」</t>
+  </si>
+  <si>
+    <t>地域</t>
+  </si>
+  <si>
+    <t>・任意
+・100文字以内</t>
+  </si>
+  <si>
+    <t>「地域は100文字以内で指定してください」</t>
+  </si>
+  <si>
+    <t>時期</t>
+  </si>
+  <si>
+    <t>・必須
+・date_format:Y-m</t>
+  </si>
+  <si>
+    <t>日数</t>
+  </si>
+  <si>
+    <t>・必須</t>
+  </si>
+  <si>
+    <t>国</t>
+  </si>
+  <si>
+    <t>目的</t>
+  </si>
+  <si>
+    <t>・任意
+・任意</t>
+  </si>
+  <si>
+    <t>スタイル</t>
+  </si>
+  <si>
+    <t>予算</t>
+  </si>
+  <si>
+    <t>旅程</t>
   </si>
 </sst>
 </file>
@@ -785,12 +836,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1355,47 +1409,47 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="51" spans="1:4">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="84" spans="1:4">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3"/>
-    </row>
-    <row r="3" ht="51" spans="1:4">
-      <c r="A3" s="3" t="s">
+      <c r="D2" s="4"/>
+    </row>
+    <row r="3" ht="68" spans="1:4">
+      <c r="A3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" ht="118" spans="1:4">
-      <c r="A4" s="3" t="s">
+      <c r="D3" s="4"/>
+    </row>
+    <row r="4" ht="84" spans="1:4">
+      <c r="A4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1406,11 +1460,11 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="24.8846153846154" customWidth="1"/>
+    <col min="2" max="2" width="24.6153846153846" customWidth="1"/>
     <col min="3" max="3" width="68.6153846153846" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1428,14 +1482,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="51" spans="1:3">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="84" spans="1:3">
+      <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1450,26 +1504,31 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" ht="68" spans="1:3">
+    <row r="4" ht="51" spans="1:2">
       <c r="A4" t="s">
         <v>16</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="5" ht="34" spans="1:3">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C5" t="s">
         <v>20</v>
       </c>
-      <c r="C5" t="s">
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
         <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1481,8 +1540,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="15.1538461538462" customWidth="1"/>
     <col min="2" max="2" width="19.2307692307692" customWidth="1"/>
@@ -1505,46 +1564,113 @@
     </row>
     <row r="2" ht="34" spans="1:3">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" ht="34" spans="1:3">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:3">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" ht="51" spans="1:3">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" ht="68" spans="1:3">
       <c r="A5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>18</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" ht="34" spans="1:3">
+      <c r="A6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" ht="34" spans="1:2">
+      <c r="A7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>40</v>
+      </c>
+      <c r="B8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" ht="21" customHeight="1" spans="1:2">
+      <c r="A10" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>47</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/docs/station4/バリデーション設計書.xlsx
+++ b/docs/station4/バリデーション設計書.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11540" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="13560" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ユーザー登録画面" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="48">
   <si>
     <t>項目</t>
   </si>
@@ -97,7 +97,8 @@
   <si>
     <t>・任意
 ・ファイル形式
-(jpg, jpeg, png, webp)</t>
+(jpg, jpeg, png, webp)
+・10MB以下</t>
   </si>
   <si>
     <t>自己紹介</t>
@@ -110,20 +111,15 @@
     <t>「自己紹介は1000文字以内で入力してください」</t>
   </si>
   <si>
-    <t>訪れた国</t>
-  </si>
-  <si>
-    <t>・任意</t>
-  </si>
-  <si>
     <t>タイトル</t>
   </si>
   <si>
     <t>・必須
+・1文字以上
 ・50文字以内</t>
   </si>
   <si>
-    <t>「タイトルは50文字以内で指定してください」</t>
+    <t>「タイトルは1文字以上50文字以内で指定してください」</t>
   </si>
   <si>
     <t>サブタイトル</t>
@@ -152,7 +148,8 @@
     <t>・任意
 ・ファイル形式
 (jpg, jpeg, png, webp)
-・上限８枚</t>
+・上限８枚
+・10MB以下</t>
   </si>
   <si>
     <t>「写真は最大８枚までです」</t>
@@ -175,6 +172,9 @@
 ・date_format:Y-m</t>
   </si>
   <si>
+    <t>選択してください</t>
+  </si>
+  <si>
     <t>日数</t>
   </si>
   <si>
@@ -192,6 +192,9 @@
   </si>
   <si>
     <t>スタイル</t>
+  </si>
+  <si>
+    <t>・任意</t>
   </si>
   <si>
     <t>予算</t>
@@ -1453,6 +1456,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
 </worksheet>
 </file>
@@ -1460,8 +1464,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelRow="3" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="2" width="24.6153846153846" customWidth="1"/>
@@ -1482,53 +1486,34 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="84" spans="1:3">
-      <c r="A2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="34" spans="1:3">
+    <row r="2" ht="34" spans="1:3">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" ht="68" spans="1:2">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" ht="51" spans="1:2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" ht="34" spans="1:3">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="34" spans="1:3">
-      <c r="A5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C4" t="s">
         <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1562,99 +1547,108 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="34" spans="1:3">
+    <row r="2" ht="51" spans="1:3">
       <c r="A2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="s">
         <v>23</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" ht="34" spans="1:3">
       <c r="A3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
         <v>26</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="4" ht="34" spans="1:3">
       <c r="A4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="2" t="s">
+    </row>
+    <row r="5" ht="84" spans="1:3">
+      <c r="A5" t="s">
         <v>30</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="5" ht="68" spans="1:3">
-      <c r="A5" t="s">
+      <c r="C5" t="s">
         <v>32</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6" ht="34" spans="1:3">
       <c r="A6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" t="s">
         <v>35</v>
       </c>
-      <c r="B6" s="3" t="s">
+    </row>
+    <row r="7" ht="34" spans="1:3">
+      <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="C6" t="s">
+      <c r="B7" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="7" ht="34" spans="1:2">
-      <c r="A7" t="s">
+      <c r="C7" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
+      <c r="B8" t="s">
         <v>40</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>42</v>
-      </c>
       <c r="B9" t="s">
-        <v>41</v>
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1" spans="1:2">
       <c r="A10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>43</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" t="s">
         <v>45</v>
-      </c>
-      <c r="B11" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -1662,7 +1656,7 @@
         <v>46</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -1670,7 +1664,7 @@
         <v>47</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/docs/station4/バリデーション設計書.xlsx
+++ b/docs/station4/バリデーション設計書.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="13560" activeTab="2"/>
+    <workbookView windowWidth="28000" windowHeight="11540"/>
   </bookViews>
   <sheets>
     <sheet name="ユーザー登録画面" sheetId="1" r:id="rId1"/>
@@ -839,15 +839,12 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1413,46 +1410,46 @@
       </c>
     </row>
     <row r="2" ht="84" spans="1:4">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="4"/>
+      <c r="D2" s="3"/>
     </row>
     <row r="3" ht="68" spans="1:4">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="4" ht="84" spans="1:4">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="4"/>
+      <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
+      <c r="A5" s="3"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1595,7 +1592,7 @@
       <c r="A6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>34</v>
       </c>
       <c r="C6" t="s">
@@ -1606,7 +1603,7 @@
       <c r="A7" t="s">
         <v>36</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>37</v>
       </c>
       <c r="C7" t="s">
@@ -1639,7 +1636,7 @@
       <c r="A10" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>43</v>
       </c>
     </row>
